--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_20-11-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_20-11-2025.xlsx
@@ -538,17 +538,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>£9.75</t>
+          <t>£9.71</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>£9.75</t>
+          <t>£9.71</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>£9.75</t>
+          <t>£9.71</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -732,17 +732,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£14.16</t>
+          <t>£14.08</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>£14.16</t>
+          <t>£14.08</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>£14.16</t>
+          <t>£14.08</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -829,17 +829,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>£14.60</t>
+          <t>£14.57</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>£14.60</t>
+          <t>£14.57</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>£14.60</t>
+          <t>£14.57</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -926,17 +926,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£18.39</t>
+          <t>£18.18</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£18.39</t>
+          <t>£18.18</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>£18.39</t>
+          <t>£18.18</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1120,17 +1120,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>£20.25</t>
+          <t>£20.32</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>£20.25</t>
+          <t>£20.32</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>£20.47</t>
+          <t>£20.32</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>£20.43</t>
+          <t>£20.50</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1217,17 +1217,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>£23.45</t>
+          <t>£23.42</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>£23.45</t>
+          <t>£23.42</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>£23.45</t>
+          <t>£23.42</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£25.20</t>
+          <t>£25.12</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>£33.00</t>
+          <t>£32.15</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1605,17 +1605,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>£30.75</t>
+          <t>£30.45</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>£30.75</t>
+          <t>£30.45</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>£30.75</t>
+          <t>£30.45</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1702,17 +1702,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>£37.70</t>
+          <t>£37.45</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>£37.70</t>
+          <t>£37.45</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>£38.05</t>
+          <t>£37.45</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1799,12 +1799,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>£38.30</t>
+          <t>£37.90</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>£38.30</t>
+          <t>£37.90</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>£27.65</t>
+          <t>£26.93</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>£27.65</t>
+          <t>£26.93</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>£33.65</t>
+          <t>£32.95</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>£33.65</t>
+          <t>£32.95</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2381,12 +2381,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>£36.80</t>
+          <t>£35.95</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>£36.80</t>
+          <t>£35.95</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2478,12 +2478,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>£41.00</t>
+          <t>£40.95</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>£41.00</t>
+          <t>£40.95</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2866,12 +2866,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>£42.90</t>
+          <t>£42.70</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>£42.90</t>
+          <t>£42.70</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>£1133.6</t>
+          <t>£1128.0</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
